--- a/public/raw-entry-data/b2c/java.xlsx
+++ b/public/raw-entry-data/b2c/java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alfa/web-alfa/tr-b2c/tech-radar/public/raw-entry-data/b2c/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFE37F8-7BDB-064C-91E8-59055F4F410F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5C4FEA-5A3A-0746-81B1-7855B09C10E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7980" yWindow="3960" windowWidth="31840" windowHeight="12300" xr2:uid="{D0E5AF86-51E4-4329-BFCB-5FE4200F8556}"/>
+    <workbookView xWindow="9880" yWindow="1980" windowWidth="31840" windowHeight="12300" xr2:uid="{D0E5AF86-51E4-4329-BFCB-5FE4200F8556}"/>
   </bookViews>
   <sheets>
     <sheet name="radar" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="138">
   <si>
     <t>Ноль</t>
   </si>
@@ -217,9 +217,6 @@
   </si>
   <si>
     <t>технологии, которые прошли боевое тестирование и готовятся перейти в актив компании.</t>
-  </si>
-  <si>
-    <t>Spring Framework</t>
   </si>
   <si>
     <t>универсальный фреймворк с открытым исходным кодом для Java-платформы. Предоставляет инструменты для создания сложных систем, например многопользовательских корпоративных веб-приложений.</t>
@@ -354,13 +351,118 @@
   </si>
   <si>
     <t>https://github.com/ben-manes/caffeine</t>
+  </si>
+  <si>
+    <t>ide</t>
+  </si>
+  <si>
+    <t>JetBrains IDEA</t>
+  </si>
+  <si>
+    <t>VS Code</t>
+  </si>
+  <si>
+    <t>OpenIDE</t>
+  </si>
+  <si>
+    <t>https://openide.ru/</t>
+  </si>
+  <si>
+    <t>https://www.npmjs.com/package/idea</t>
+  </si>
+  <si>
+    <t>https://www.npmjs.com/package/vs code</t>
+  </si>
+  <si>
+    <t>Бесплатная IDE на базе IntelliJ IDEA Platform с открытым исходным кодом</t>
+  </si>
+  <si>
+    <t>IntelliJ IDEA — это IDE от JetBrains</t>
+  </si>
+  <si>
+    <t>VS Code (Visual Studio Code) — это редактор кода от Microsoft</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>Testcontainers</t>
+  </si>
+  <si>
+    <t>https://testcontainers.com/</t>
+  </si>
+  <si>
+    <t>Библиотека с открытым исходным кодом для автоматического управления Docker-контейнерами во время выполнения интеграционных тестов</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>https://www.usebruno.com/</t>
+  </si>
+  <si>
+    <t>Клиент с открытым исходным кодом для тестирования и разработки REST, GraphQL и gRPC API</t>
+  </si>
+  <si>
+    <t>gRPC</t>
+  </si>
+  <si>
+    <t>https://grpc.io/</t>
+  </si>
+  <si>
+    <t>Фреймворк с открытым исходным кодом, разработанный Google для удаленного вызова процедур (RPC)</t>
+  </si>
+  <si>
+    <t>Приложение с открытым исходным кодом, которое предоставляет локальную среду для разработки, управления контейнерами (Docker/containerd)</t>
+  </si>
+  <si>
+    <t>Rancher</t>
+  </si>
+  <si>
+    <t>docker</t>
+  </si>
+  <si>
+    <t>https://rancherdesktop.io/</t>
+  </si>
+  <si>
+    <t>Набор инструментов для быстрого построения сложных распределенных систем и микросервисов на базе Spring Boot</t>
+  </si>
+  <si>
+    <t>Библиотека реактивного программирования для Java, ориентированная на создание неблокирующих приложений с высокой производительностью</t>
+  </si>
+  <si>
+    <t>Spring Boot</t>
+  </si>
+  <si>
+    <t>Spring Cloud</t>
+  </si>
+  <si>
+    <t>Project Reactor</t>
+  </si>
+  <si>
+    <t>Project Loom</t>
+  </si>
+  <si>
+    <t>reactor</t>
+  </si>
+  <si>
+    <t>https://spring.io/projects/spring-cloud</t>
+  </si>
+  <si>
+    <t>https://projectreactor.io/</t>
+  </si>
+  <si>
+    <t>https://openjdk.org/projects/loom/</t>
+  </si>
+  <si>
+    <t>Это инициатива OpenJDK, направленная на кардинальное улучшение многопоточности в Java за счет внедрения легковесных "виртуальных потоков"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -406,8 +508,16 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,8 +529,20 @@
         <fgColor theme="4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4C6E7"/>
+        <bgColor rgb="FFB4C6E7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -443,6 +565,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF8EA9DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -453,7 +590,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1" applyProtection="1"/>
@@ -469,6 +606,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Акцент1" xfId="1" builtinId="29"/>
@@ -828,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E083F0B-9B6B-4AE1-B88F-228D13850335}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
@@ -876,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
@@ -893,13 +1036,13 @@
     </row>
     <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E3" t="s">
         <v>54</v>
@@ -908,18 +1051,18 @@
         <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>54</v>
@@ -928,18 +1071,18 @@
         <v>5</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" t="s">
         <v>67</v>
       </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>4</v>
@@ -948,7 +1091,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1073,13 +1216,13 @@
     </row>
     <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
         <v>72</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>54</v>
@@ -1088,18 +1231,18 @@
         <v>5</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="E13" t="s">
         <v>54</v>
@@ -1108,18 +1251,18 @@
         <v>56</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
         <v>54</v>
@@ -1128,18 +1271,18 @@
         <v>56</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="E15" t="s">
         <v>54</v>
@@ -1148,18 +1291,18 @@
         <v>56</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
         <v>4</v>
@@ -1168,18 +1311,18 @@
         <v>5</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
         <v>54</v>
@@ -1188,18 +1331,18 @@
         <v>5</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="E18" t="s">
         <v>54</v>
@@ -1208,18 +1351,18 @@
         <v>5</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
         <v>90</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="E19" t="s">
         <v>54</v>
@@ -1228,18 +1371,18 @@
         <v>5</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
         <v>54</v>
@@ -1248,18 +1391,18 @@
         <v>5</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
         <v>54</v>
@@ -1268,7 +1411,207 @@
         <v>56</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>5</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1291,11 +1634,17 @@
     <hyperlink ref="D18" r:id="rId16" xr:uid="{1D251410-AE32-7840-88C5-58A044D16C79}"/>
     <hyperlink ref="D20" r:id="rId17" xr:uid="{C78CA9BC-589C-974D-AB61-291F2960A857}"/>
     <hyperlink ref="D21" r:id="rId18" xr:uid="{D97DB915-967A-E540-AF0D-821CCF37E95C}"/>
+    <hyperlink ref="D24" r:id="rId19" xr:uid="{DDE46E74-3168-3347-B146-1AC9110E39A6}"/>
+    <hyperlink ref="D22" r:id="rId20" xr:uid="{C5C96EC2-2900-534C-826C-CACE3C0E0CEE}"/>
+    <hyperlink ref="D23" r:id="rId21" xr:uid="{18C62945-7703-2C48-9C49-5417D7FDD0F6}"/>
+    <hyperlink ref="D27" r:id="rId22" xr:uid="{2FF7A589-37D0-D94B-A936-39DF720EEBF8}"/>
+    <hyperlink ref="D29" r:id="rId23" xr:uid="{1A33E183-0CC6-324F-B520-17165594494A}"/>
+    <hyperlink ref="D30" r:id="rId24" xr:uid="{7065D825-33DA-AF42-966B-FED7BF73E86C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId25"/>
   <tableParts count="1">
-    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId26"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -1304,25 +1653,25 @@
           <x14:formula1>
             <xm:f>meta!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>F22:F77</xm:sqref>
+          <xm:sqref>F32:F77</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6857320C-10DD-4851-98FA-A3CA686293DC}">
           <x14:formula1>
             <xm:f>meta!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>E22:E74</xm:sqref>
+          <xm:sqref>E32:E74</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5AFEE91B-7A0C-0045-8A32-2A47382063B4}">
           <x14:formula1>
             <xm:f>rings!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F5 F13:F21</xm:sqref>
+          <xm:sqref>F2:F5 F13:F21 F25 F27 F29:F31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6E5D21C0-46D9-574F-924F-47FF86B1D17A}">
           <x14:formula1>
             <xm:f>quadrants!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E5 E12:E21</xm:sqref>
+          <xm:sqref>E2:E5 E12:E26 E28:E31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ECCB302B-B329-497F-B6B4-042AE8F9E14B}">
           <x14:formula1>
